--- a/artfynd/A 63387-2025 artfynd.xlsx
+++ b/artfynd/A 63387-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99410517</v>
+        <v>99410405</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576164.4060912454</v>
+        <v>576175</v>
       </c>
       <c r="R2" t="n">
-        <v>6442749.229862698</v>
+        <v>6442723</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-02-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-02-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>99410467</v>
       </c>
       <c r="B3" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576166.094784345</v>
+        <v>576166</v>
       </c>
       <c r="R3" t="n">
-        <v>6442743.97864429</v>
+        <v>6442744</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-02-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-02-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>99410517</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skjåsjön, Stjälkhammar, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>576164</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6442749</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-02-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
